--- a/nr-update-transactions/ig/StructureDefinition-EventCode.xlsx
+++ b/nr-update-transactions/ig/StructureDefinition-EventCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T15:05:22+00:00</t>
+    <t>2026-06-24T15:07:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-transactions/ig/StructureDefinition-EventCode.xlsx
+++ b/nr-update-transactions/ig/StructureDefinition-EventCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T15:07:04+00:00</t>
+    <t>2026-06-24T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-transactions/ig/StructureDefinition-EventCode.xlsx
+++ b/nr-update-transactions/ig/StructureDefinition-EventCode.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T15:07:59+00:00</t>
+    <t>2026-06-24T15:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
